--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EDEBAA-C206-4939-8094-6CCB9A34AA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5E87EF6-83A8-4DA4-869B-7BDE550E9DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5571E39-E924-4AEA-A73C-8E06B7F8C5CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B60926E-4352-4978-994C-CDECBC9C06A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>ncap_af~fx</t>
   </si>
   <si>
-    <t>ep_bioenergy_w113757307-220_HRV__irena</t>
+    <t>ep_bioenergy_Kutina_HRV__irena</t>
   </si>
   <si>
     <t>HRV</t>
@@ -98,55 +98,55 @@
     <t>bioenergy</t>
   </si>
   <si>
-    <t>e_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w162022271-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w170366194-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w210745193-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w273326173-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w43337263-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w89817617-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w89819945-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w96704507-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV</t>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Ogulin_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Pula_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Sesvete_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Sibenik_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Sisak_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Split_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Vinkovci_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_Viskovo_HRV__irena</t>
+  </si>
+  <si>
+    <t>e_Viskovo_HRV</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000108045</t>
@@ -161,7 +161,7 @@
     <t>gas</t>
   </si>
   <si>
-    <t>e_w89818719-400_HRV,h_w89818719-400_HRV</t>
+    <t>e_VelikaGorica_HRV,h_VelikaGorica_HRV</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400050-CHP</t>
@@ -170,7 +170,7 @@
     <t>ep_gas_combined_cycle_G100000400052-CHP</t>
   </si>
   <si>
-    <t>e_w89820062-400_HRV,h_w89820062-400_HRV</t>
+    <t>e_Zagreb_HRV,h_Zagreb_HRV</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100001031110-CHP</t>
@@ -179,7 +179,7 @@
     <t>ep_gas_steam_turbine_G100000400055-CHP</t>
   </si>
   <si>
-    <t>e_w96704507-220_HRV,h_w96704507-220_HRV</t>
+    <t>e_Kutina_HRV,h_Kutina_HRV</t>
   </si>
   <si>
     <t>ep_geothermal_G100001030295</t>
@@ -194,18 +194,36 @@
     <t>ep_geothermal_G100001048252</t>
   </si>
   <si>
-    <t>e_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>ep_geothermal_w89820062-400_HRV</t>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>ep_geothermal_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>ep_hydro_Knin_HRV__irena</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV</t>
+  </si>
+  <si>
+    <t>ep_hydro_Ogulin_HRV__irena</t>
+  </si>
+  <si>
+    <t>ep_hydro_Split_HRV__irena</t>
+  </si>
+  <si>
+    <t>ep_hydro_Viskovo_HRV__irena</t>
+  </si>
+  <si>
+    <t>ep_hydro_Zagreb_HRV__irena</t>
   </si>
   <si>
     <t>ep_hydro_dam_G100000601477</t>
   </si>
   <si>
-    <t>hydro</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000601478</t>
   </si>
   <si>
@@ -227,9 +245,6 @@
     <t>ep_hydro_ps_G100000601481</t>
   </si>
   <si>
-    <t>e_w163860997-400_HRV</t>
-  </si>
-  <si>
     <t>ep_hydro_ps_G100000601482</t>
   </si>
   <si>
@@ -251,21 +266,6 @@
     <t>ep_hydro_ror_G100001092825</t>
   </si>
   <si>
-    <t>ep_hydro_w163860997-400_HRV__irena</t>
-  </si>
-  <si>
-    <t>ep_hydro_w273326173-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>ep_hydro_w43337263-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>ep_hydro_w89817617-220_HRV__irena</t>
-  </si>
-  <si>
-    <t>ep_hydro_w89820062-400_HRV__irena</t>
-  </si>
-  <si>
     <t>ep_m_coal_subcritical_G100000108044</t>
   </si>
   <si>
@@ -275,13 +275,13 @@
     <t>oil</t>
   </si>
   <si>
-    <t>e_w170366194-220_HRV,h_w170366194-220_HRV</t>
+    <t>e_Sisak_HRV,h_Sisak_HRV</t>
   </si>
   <si>
     <t>ep_oil_combined_cycle_G100000400058-CHP</t>
   </si>
   <si>
-    <t>e_w89819945-220_HRV,h_w89819945-220_HRV</t>
+    <t>e_Sesvete_HRV,h_Sesveth_HRV</t>
   </si>
   <si>
     <t>ep_oil_combined_cycle_G100000400059-CHP</t>
@@ -293,7 +293,7 @@
     <t>ep_oil_gas_turbine_G100000400053-CHP</t>
   </si>
   <si>
-    <t>e_w89823918-400_HRV,h_w89823918-400_HRV</t>
+    <t>e_Osijek_HRV,h_Osijek_HRV</t>
   </si>
   <si>
     <t>ep_oil_gas_turbine_G100000400054-CHP</t>
@@ -497,6 +497,21 @@
     <t>Draškovec geothermal power plant_3 -- operating</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/163860997-400_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/273326173-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/43337263-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89817617-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/89820062-400_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
     <t>Orlovac hydroelectric plant_ -- operating</t>
   </si>
   <si>
@@ -545,21 +560,6 @@
     <t>Rijeka hydroelectric plant_ -- operating</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/163860997-400_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/273326173-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/43337263-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89817617-220_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/89820062-400_Missing Hydro Capacity -- operating</t>
-  </si>
-  <si>
     <t>Plomin power station_Phase A -- mothballed</t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_w89818719-400_HRV</t>
+    <t>e_VelikaGorica_HRV</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
@@ -776,7 +776,7 @@
     <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_w89823918-400_HRV</t>
+    <t>e_Osijek_HRV</t>
   </si>
   <si>
     <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
@@ -1201,7 +1201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA38009-6C97-4F4C-A2D4-17B7B663B798}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CFA44F-C018-4923-8EFC-4235BE13B709}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1286,7 +1286,7 @@
         <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11">
         <v>0.17299880000000001</v>
@@ -1596,7 +1596,7 @@
         <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F16">
         <v>0.27938750000000001</v>
@@ -1658,7 +1658,7 @@
         <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17">
         <v>9.3936000000000006E-2</v>
@@ -1720,7 +1720,7 @@
         <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>0.48667500000000002</v>
@@ -1782,7 +1782,7 @@
         <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F19">
         <v>0.450625</v>
@@ -1844,7 +1844,7 @@
         <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <v>0.450625</v>
@@ -1906,7 +1906,7 @@
         <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F21">
         <v>0.32445000000000002</v>
@@ -2154,7 +2154,7 @@
         <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F25">
         <v>0.28839999999999999</v>
@@ -2211,7 +2211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B8377A-E401-4EFE-B249-C545ECD77090}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2570688-84CA-4000-A086-E3EA27D391DF}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2299,7 +2299,7 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>2025</v>
@@ -2323,7 +2323,7 @@
         <v>100</v>
       </c>
       <c r="Q11" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="R11" t="s">
         <v>185</v>
@@ -3191,7 +3191,7 @@
         <v>0.1251653949323632</v>
       </c>
       <c r="Q25" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="R25" t="s">
         <v>201</v>
@@ -3223,7 +3223,7 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F26">
         <v>2028</v>
@@ -3459,7 +3459,7 @@
         <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F30">
         <v>2025</v>
@@ -3518,7 +3518,7 @@
         <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F31">
         <v>2025</v>
@@ -4358,7 +4358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A271A683-3FD3-47E3-92D5-AEB0118C4567}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECFB1B79-EA65-4209-BDA6-F7561AA2A4BE}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4455,10 +4455,10 @@
         <v>2022</v>
       </c>
       <c r="G11">
-        <v>3.0239130434782616E-2</v>
+        <v>1.6282608695652175E-2</v>
       </c>
       <c r="H11">
-        <v>0.32959999999999995</v>
+        <v>0.3296</v>
       </c>
       <c r="I11">
         <v>5197.5</v>
@@ -4868,10 +4868,10 @@
         <v>2022</v>
       </c>
       <c r="G18">
-        <v>1.6282608695652175E-2</v>
+        <v>3.0239130434782616E-2</v>
       </c>
       <c r="H18">
-        <v>0.3296</v>
+        <v>0.32959999999999995</v>
       </c>
       <c r="I18">
         <v>5197.5</v>
@@ -4980,7 +4980,7 @@
         <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F20">
         <v>2000</v>
@@ -5364,7 +5364,7 @@
         <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F26">
         <v>2028</v>
@@ -5423,7 +5423,7 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F27">
         <v>2019</v>
@@ -5600,28 +5600,19 @@
         <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F30">
-        <v>1973</v>
+        <v>2022</v>
       </c>
       <c r="G30">
-        <v>0.23699999999999999</v>
+        <v>2.771003717472121E-2</v>
       </c>
       <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>3162.5000000000005</v>
-      </c>
-      <c r="J30">
-        <v>60.500000000000014</v>
-      </c>
-      <c r="K30">
-        <v>2.3100000000000005</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="Q30" t="s">
         <v>134</v>
@@ -5645,12 +5636,12 @@
         <v>138</v>
       </c>
       <c r="X30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
@@ -5659,34 +5650,25 @@
         <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>1965</v>
+        <v>2022</v>
       </c>
       <c r="G31">
-        <v>0.216</v>
+        <v>8.7863909541511825E-2</v>
       </c>
       <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>3162.5000000000005</v>
-      </c>
-      <c r="J31">
-        <v>60.500000000000014</v>
-      </c>
-      <c r="K31">
-        <v>2.3100000000000005</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="Q31" t="s">
         <v>134</v>
       </c>
       <c r="R31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S31" t="s">
         <v>16</v>
@@ -5704,12 +5686,12 @@
         <v>138</v>
       </c>
       <c r="X31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -5718,34 +5700,25 @@
         <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>1975</v>
+        <v>2022</v>
       </c>
       <c r="G32">
-        <v>9.5000000000000001E-2</v>
+        <v>0.21382912019826533</v>
       </c>
       <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>3162.5000000000005</v>
-      </c>
-      <c r="J32">
-        <v>60.500000000000007</v>
-      </c>
-      <c r="K32">
-        <v>2.3100000000000005</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="Q32" t="s">
         <v>134</v>
       </c>
       <c r="R32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S32" t="s">
         <v>16</v>
@@ -5763,12 +5736,12 @@
         <v>138</v>
       </c>
       <c r="X32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
@@ -5777,34 +5750,25 @@
         <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F33">
-        <v>1961</v>
+        <v>2022</v>
       </c>
       <c r="G33">
-        <v>0.53800000000000003</v>
+        <v>1.4663228004956638E-2</v>
       </c>
       <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
-        <v>2750</v>
-      </c>
-      <c r="J33">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="K33">
-        <v>2.1</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="Q33" t="s">
         <v>134</v>
       </c>
       <c r="R33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S33" t="s">
         <v>16</v>
@@ -5822,12 +5786,12 @@
         <v>138</v>
       </c>
       <c r="X33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
         <v>16</v>
@@ -5836,34 +5800,25 @@
         <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F34">
-        <v>1954</v>
+        <v>2022</v>
       </c>
       <c r="G34">
-        <v>5.6000000000000001E-2</v>
+        <v>2.863370508054525E-2</v>
       </c>
       <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34">
-        <v>3162.5000000000005</v>
-      </c>
-      <c r="J34">
-        <v>60.500000000000014</v>
-      </c>
-      <c r="K34">
-        <v>2.31</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N34">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="Q34" t="s">
         <v>134</v>
       </c>
       <c r="R34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S34" t="s">
         <v>16</v>
@@ -5881,12 +5836,12 @@
         <v>138</v>
       </c>
       <c r="X34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -5895,25 +5850,25 @@
         <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>2015</v>
+        <v>1973</v>
       </c>
       <c r="G35">
-        <v>4.2000000000000003E-2</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>3712.5000000000009</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="J35">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="K35">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -5922,7 +5877,7 @@
         <v>134</v>
       </c>
       <c r="R35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S35" t="s">
         <v>16</v>
@@ -5945,7 +5900,7 @@
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
         <v>16</v>
@@ -5954,25 +5909,25 @@
         <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F36">
-        <v>2028</v>
+        <v>1965</v>
       </c>
       <c r="G36">
-        <v>3.5000000000000003E-2</v>
+        <v>0.216</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="J36">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="K36">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="N36">
         <v>100</v>
@@ -5981,7 +5936,7 @@
         <v>134</v>
       </c>
       <c r="R36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S36" t="s">
         <v>16</v>
@@ -6004,46 +5959,49 @@
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
       </c>
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F37">
-        <v>1984</v>
+        <v>1975</v>
       </c>
       <c r="G37">
-        <v>0.24</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>2277</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="J37">
-        <v>48.400000000000006</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="K37">
-        <v>1.7325000000000002</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="Q37" t="s">
+        <v>134</v>
+      </c>
+      <c r="R37" t="s">
+        <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>16</v>
+      </c>
+      <c r="T37" t="s">
         <v>158</v>
-      </c>
-      <c r="R37" t="s">
-        <v>60</v>
-      </c>
-      <c r="S37" t="s">
-        <v>16</v>
-      </c>
-      <c r="T37" t="s">
-        <v>159</v>
       </c>
       <c r="U37" t="s">
         <v>136</v>
@@ -6065,32 +6023,35 @@
       <c r="C38" t="s">
         <v>16</v>
       </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
       <c r="E38" t="s">
         <v>30</v>
       </c>
       <c r="F38">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="G38">
-        <v>0.09</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>2277</v>
+        <v>2750</v>
       </c>
       <c r="J38">
-        <v>48.400000000000013</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="K38">
-        <v>1.7325000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="N38">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q38" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="R38" t="s">
         <v>62</v>
@@ -6099,7 +6060,7 @@
         <v>16</v>
       </c>
       <c r="T38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U38" t="s">
         <v>136</v>
@@ -6125,28 +6086,28 @@
         <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F39">
-        <v>1982</v>
+        <v>1954</v>
       </c>
       <c r="G39">
-        <v>7.6999999999999999E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>2783</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="J39">
-        <v>66.550000000000011</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="K39">
-        <v>2.8875000000000002</v>
+        <v>2.31</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q39" t="s">
         <v>134</v>
@@ -6158,7 +6119,7 @@
         <v>16</v>
       </c>
       <c r="T39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U39" t="s">
         <v>136</v>
@@ -6184,25 +6145,25 @@
         <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>1989</v>
+        <v>2015</v>
       </c>
       <c r="G40">
-        <v>7.5999999999999998E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>2783</v>
+        <v>3712.5000000000009</v>
       </c>
       <c r="J40">
-        <v>66.550000000000011</v>
+        <v>71.5</v>
       </c>
       <c r="K40">
-        <v>2.8875000000000002</v>
+        <v>2.52</v>
       </c>
       <c r="N40">
         <v>100</v>
@@ -6217,7 +6178,7 @@
         <v>16</v>
       </c>
       <c r="T40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U40" t="s">
         <v>136</v>
@@ -6243,28 +6204,28 @@
         <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F41">
-        <v>1912</v>
+        <v>2028</v>
       </c>
       <c r="G41">
-        <v>4.5999999999999999E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>3267.0000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="J41">
-        <v>78.650000000000006</v>
+        <v>71.5</v>
       </c>
       <c r="K41">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="N41">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="Q41" t="s">
         <v>134</v>
@@ -6276,7 +6237,7 @@
         <v>16</v>
       </c>
       <c r="T41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U41" t="s">
         <v>136</v>
@@ -6298,35 +6259,32 @@
       <c r="C42" t="s">
         <v>16</v>
       </c>
-      <c r="D42" t="s">
-        <v>53</v>
-      </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F42">
-        <v>2015</v>
+        <v>1984</v>
       </c>
       <c r="G42">
-        <v>4.1000000000000002E-2</v>
+        <v>0.24</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>3267.0000000000009</v>
+        <v>2277</v>
       </c>
       <c r="J42">
-        <v>78.650000000000006</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="K42">
-        <v>3.1500000000000004</v>
+        <v>1.7325000000000002</v>
       </c>
       <c r="N42">
         <v>100</v>
       </c>
       <c r="Q42" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="R42" t="s">
         <v>66</v>
@@ -6357,35 +6315,32 @@
       <c r="C43" t="s">
         <v>16</v>
       </c>
-      <c r="D43" t="s">
-        <v>53</v>
-      </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F43">
-        <v>2010</v>
+        <v>1952</v>
       </c>
       <c r="G43">
-        <v>4.2000000000000003E-2</v>
+        <v>0.09</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>3267.0000000000009</v>
+        <v>2277</v>
       </c>
       <c r="J43">
-        <v>78.650000000000006</v>
+        <v>48.400000000000013</v>
       </c>
       <c r="K43">
-        <v>3.1500000000000004</v>
+        <v>1.7325000000000002</v>
       </c>
       <c r="N43">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q43" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="R43" t="s">
         <v>67</v>
@@ -6420,25 +6375,25 @@
         <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F44">
-        <v>1968</v>
+        <v>1982</v>
       </c>
       <c r="G44">
-        <v>3.6999999999999998E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>3267.0000000000005</v>
+        <v>2783</v>
       </c>
       <c r="J44">
-        <v>78.650000000000006</v>
+        <v>66.550000000000011</v>
       </c>
       <c r="K44">
-        <v>3.1500000000000004</v>
+        <v>2.8875000000000002</v>
       </c>
       <c r="N44">
         <v>100</v>
@@ -6479,19 +6434,28 @@
         <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F45">
-        <v>2022</v>
+        <v>1989</v>
       </c>
       <c r="G45">
-        <v>2.771003717472121E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="H45">
-        <v>0.33123000000000008</v>
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>2783</v>
+      </c>
+      <c r="J45">
+        <v>66.550000000000011</v>
+      </c>
+      <c r="K45">
+        <v>2.8875000000000002</v>
       </c>
       <c r="N45">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="Q45" t="s">
         <v>134</v>
@@ -6515,7 +6479,7 @@
         <v>138</v>
       </c>
       <c r="X45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.45">
@@ -6529,19 +6493,28 @@
         <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F46">
-        <v>2022</v>
+        <v>1912</v>
       </c>
       <c r="G46">
-        <v>8.7863909541511825E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="H46">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>3267.0000000000005</v>
+      </c>
+      <c r="J46">
+        <v>78.650000000000006</v>
+      </c>
+      <c r="K46">
+        <v>3.15</v>
       </c>
       <c r="N46">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="Q46" t="s">
         <v>134</v>
@@ -6565,7 +6538,7 @@
         <v>138</v>
       </c>
       <c r="X46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.45">
@@ -6579,19 +6552,28 @@
         <v>53</v>
       </c>
       <c r="E47" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F47">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="G47">
-        <v>0.21382912019826533</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="H47">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>3267.0000000000009</v>
+      </c>
+      <c r="J47">
+        <v>78.650000000000006</v>
+      </c>
+      <c r="K47">
+        <v>3.1500000000000004</v>
       </c>
       <c r="N47">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="Q47" t="s">
         <v>134</v>
@@ -6615,7 +6597,7 @@
         <v>138</v>
       </c>
       <c r="X47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.45">
@@ -6629,19 +6611,28 @@
         <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F48">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="G48">
-        <v>1.4663228004956638E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="H48">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>3267.0000000000009</v>
+      </c>
+      <c r="J48">
+        <v>78.650000000000006</v>
+      </c>
+      <c r="K48">
+        <v>3.1500000000000004</v>
       </c>
       <c r="N48">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="Q48" t="s">
         <v>134</v>
@@ -6665,7 +6656,7 @@
         <v>138</v>
       </c>
       <c r="X48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.45">
@@ -6679,19 +6670,28 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F49">
-        <v>2022</v>
+        <v>1968</v>
       </c>
       <c r="G49">
-        <v>2.863370508054525E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="H49">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>3267.0000000000005</v>
+      </c>
+      <c r="J49">
+        <v>78.650000000000006</v>
+      </c>
+      <c r="K49">
+        <v>3.1500000000000004</v>
       </c>
       <c r="N49">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="Q49" t="s">
         <v>134</v>
@@ -6715,7 +6715,7 @@
         <v>138</v>
       </c>
       <c r="X49" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.45">
@@ -6729,7 +6729,7 @@
         <v>36</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F50">
         <v>1969</v>
@@ -7234,7 +7234,7 @@
         <v>76</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F58">
         <v>1978</v>
@@ -7736,7 +7736,7 @@
         <v>16</v>
       </c>
       <c r="T66" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U66" t="s">
         <v>136</v>
@@ -7798,7 +7798,7 @@
         <v>16</v>
       </c>
       <c r="T67" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U67" t="s">
         <v>136</v>
@@ -8542,7 +8542,7 @@
         <v>16</v>
       </c>
       <c r="T79" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U79" t="s">
         <v>136</v>
@@ -8604,7 +8604,7 @@
         <v>16</v>
       </c>
       <c r="T80" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U80" t="s">
         <v>136</v>
@@ -10318,7 +10318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63337554-ED74-4ECE-92FE-24CA833F3EB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6446E7-D9B5-4B6D-9367-C7EF08C09901}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5E87EF6-83A8-4DA4-869B-7BDE550E9DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67BB18B5-A0CF-4CED-B09C-1FB072D45393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B60926E-4352-4978-994C-CDECBC9C06A6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C9BC4828-996B-4909-B02B-E8E58C5A1B11}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="269">
   <si>
     <t>~fi_t</t>
   </si>
@@ -740,10 +740,13 @@
     <t>ep_coal_subcritical_G100000108045_ccs-rf</t>
   </si>
   <si>
+    <t>e_Pula_HRV,CO2Cap</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_VelikaGorica_HRV</t>
+    <t>e_VelikaGorica_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
@@ -752,21 +755,33 @@
     <t>ep_gas_combined_cycle_G100000400052-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>e_Zagreb_HRV,CO2Cap</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100001031110-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_steam_turbine_G100000400055-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>e_Kutina_HRV,CO2Cap</t>
+  </si>
+  <si>
     <t>ep_m_coal_subcritical_G100000108044_ccs-rf</t>
   </si>
   <si>
     <t>ep_oil_combined_cycle_G100000400056-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>e_Sisak_HRV,CO2Cap</t>
+  </si>
+  <si>
     <t>ep_oil_combined_cycle_G100000400058-CHP_ccs-rf</t>
   </si>
   <si>
+    <t>e_Sesvete_HRV,CO2Cap</t>
+  </si>
+  <si>
     <t>ep_oil_combined_cycle_G100000400059-CHP_ccs-rf</t>
   </si>
   <si>
@@ -776,7 +791,7 @@
     <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Osijek_HRV</t>
+    <t>e_Osijek_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
@@ -786,6 +801,9 @@
   </si>
   <si>
     <t>ep_oil_steam_turbine_G100001031130_ccs-rf</t>
+  </si>
+  <si>
+    <t>e_Viskovo_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ccs retrofit of -- Plomin power station_Phase B -- operating</t>
@@ -1201,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CFA44F-C018-4923-8EFC-4235BE13B709}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA7783B-A41C-44A0-853C-4AC410202BEF}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1286,7 +1304,7 @@
         <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="F11">
         <v>0.17299880000000001</v>
@@ -1322,7 +1340,7 @@
         <v>16</v>
       </c>
       <c r="R11" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="S11" t="s">
         <v>136</v>
@@ -1339,7 +1357,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -1348,7 +1366,7 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12">
         <v>0.52272499999999988</v>
@@ -1375,16 +1393,16 @@
         <v>20</v>
       </c>
       <c r="O12" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q12" t="s">
         <v>16</v>
       </c>
       <c r="R12" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="S12" t="s">
         <v>136</v>
@@ -1401,7 +1419,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1410,7 +1428,7 @@
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F13">
         <v>0.43259999999999998</v>
@@ -1437,16 +1455,16 @@
         <v>20</v>
       </c>
       <c r="O13" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q13" t="s">
         <v>16</v>
       </c>
       <c r="R13" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="S13" t="s">
         <v>136</v>
@@ -1463,7 +1481,7 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1472,7 +1490,7 @@
         <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="F14">
         <v>0.34247500000000003</v>
@@ -1499,16 +1517,16 @@
         <v>20</v>
       </c>
       <c r="O14" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q14" t="s">
         <v>16</v>
       </c>
       <c r="R14" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="S14" t="s">
         <v>136</v>
@@ -1525,7 +1543,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -1534,7 +1552,7 @@
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F15">
         <v>0.32445000000000002</v>
@@ -1561,16 +1579,16 @@
         <v>20</v>
       </c>
       <c r="O15" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q15" t="s">
         <v>16</v>
       </c>
       <c r="R15" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="S15" t="s">
         <v>136</v>
@@ -1587,7 +1605,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -1596,7 +1614,7 @@
         <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F16">
         <v>0.27938750000000001</v>
@@ -1623,16 +1641,16 @@
         <v>20</v>
       </c>
       <c r="O16" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q16" t="s">
         <v>16</v>
       </c>
       <c r="R16" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="S16" t="s">
         <v>136</v>
@@ -1649,7 +1667,7 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -1658,7 +1676,7 @@
         <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="F17">
         <v>9.3936000000000006E-2</v>
@@ -1688,13 +1706,13 @@
         <v>134</v>
       </c>
       <c r="P17" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q17" t="s">
         <v>16</v>
       </c>
       <c r="R17" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="S17" t="s">
         <v>136</v>
@@ -1711,7 +1729,7 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -1720,7 +1738,7 @@
         <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>243</v>
       </c>
       <c r="F18">
         <v>0.48667500000000002</v>
@@ -1747,16 +1765,16 @@
         <v>20</v>
       </c>
       <c r="O18" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P18" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q18" t="s">
         <v>16</v>
       </c>
       <c r="R18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="S18" t="s">
         <v>136</v>
@@ -1773,7 +1791,7 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -1782,7 +1800,7 @@
         <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="F19">
         <v>0.450625</v>
@@ -1809,16 +1827,16 @@
         <v>20</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q19" t="s">
         <v>16</v>
       </c>
       <c r="R19" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="S19" t="s">
         <v>136</v>
@@ -1835,7 +1853,7 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -1844,7 +1862,7 @@
         <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="F20">
         <v>0.450625</v>
@@ -1871,16 +1889,16 @@
         <v>20</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q20" t="s">
         <v>16</v>
       </c>
       <c r="R20" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="S20" t="s">
         <v>136</v>
@@ -1897,7 +1915,7 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -1906,7 +1924,7 @@
         <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="F21">
         <v>0.32445000000000002</v>
@@ -1933,16 +1951,16 @@
         <v>20</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P21" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q21" t="s">
         <v>16</v>
       </c>
       <c r="R21" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="S21" t="s">
         <v>136</v>
@@ -1959,7 +1977,7 @@
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
@@ -1968,7 +1986,7 @@
         <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F22">
         <v>0.20728750000000001</v>
@@ -1995,16 +2013,16 @@
         <v>20</v>
       </c>
       <c r="O22" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P22" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q22" t="s">
         <v>16</v>
       </c>
       <c r="R22" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="S22" t="s">
         <v>136</v>
@@ -2021,7 +2039,7 @@
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -2030,7 +2048,7 @@
         <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F23">
         <v>0.1892625</v>
@@ -2057,16 +2075,16 @@
         <v>20</v>
       </c>
       <c r="O23" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P23" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q23" t="s">
         <v>16</v>
       </c>
       <c r="R23" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="S23" t="s">
         <v>136</v>
@@ -2083,7 +2101,7 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -2092,7 +2110,7 @@
         <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F24">
         <v>0.1892625</v>
@@ -2119,16 +2137,16 @@
         <v>20</v>
       </c>
       <c r="O24" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="P24" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="s">
         <v>16</v>
       </c>
       <c r="R24" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="S24" t="s">
         <v>136</v>
@@ -2145,7 +2163,7 @@
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -2154,7 +2172,7 @@
         <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="F25">
         <v>0.28839999999999999</v>
@@ -2184,13 +2202,13 @@
         <v>134</v>
       </c>
       <c r="P25" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q25" t="s">
         <v>16</v>
       </c>
       <c r="R25" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="S25" t="s">
         <v>136</v>
@@ -2211,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2570688-84CA-4000-A086-E3EA27D391DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD273874-C7CC-4080-9F69-7AC3919C7021}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4358,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECFB1B79-EA65-4209-BDA6-F7561AA2A4BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B1C8DF-6F9E-43CD-B7AE-0B99CF73CBAD}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10318,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6446E7-D9B5-4B6D-9367-C7EF08C09901}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6BB0DA-E733-4C7F-8000-F4FCDC56EFEA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67BB18B5-A0CF-4CED-B09C-1FB072D45393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3403F802-8D0D-4B55-BB39-7EF723568CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C9BC4828-996B-4909-B02B-E8E58C5A1B11}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{67C0CEAE-C021-4873-8EA5-5762788245BB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA7783B-A41C-44A0-853C-4AC410202BEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4282D65-110E-4440-B10B-F484E4ABB221}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2229,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD273874-C7CC-4080-9F69-7AC3919C7021}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED9FECF-1F0A-4BCE-9843-357054952346}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4376,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B1C8DF-6F9E-43CD-B7AE-0B99CF73CBAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2BA984-850C-4AB2-A92B-58BEE4DF1603}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7568,7 +7568,7 @@
         <v>16</v>
       </c>
       <c r="T63" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U63" t="s">
         <v>136</v>
@@ -7630,7 +7630,7 @@
         <v>16</v>
       </c>
       <c r="T64" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U64" t="s">
         <v>136</v>
@@ -7754,7 +7754,7 @@
         <v>16</v>
       </c>
       <c r="T66" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U66" t="s">
         <v>136</v>
@@ -7816,7 +7816,7 @@
         <v>16</v>
       </c>
       <c r="T67" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U67" t="s">
         <v>136</v>
@@ -8560,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="T79" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U79" t="s">
         <v>136</v>
@@ -8622,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="T80" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U80" t="s">
         <v>136</v>
@@ -9433,7 +9433,7 @@
         <v>33</v>
       </c>
       <c r="O100">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.45">
@@ -9462,7 +9462,7 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.45">
@@ -9491,7 +9491,7 @@
         <v>33</v>
       </c>
       <c r="O102">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451533</v>
       </c>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.45">
@@ -10336,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6BB0DA-E733-4C7F-8000-F4FCDC56EFEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E97075-98E3-41F3-B6EB-10D10949CFEE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3403F802-8D0D-4B55-BB39-7EF723568CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0C31763-B926-4AF3-A75C-4DFEC4D4DFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{67C0CEAE-C021-4873-8EA5-5762788245BB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01D61C49-94EB-47B1-B781-E71D41C62138}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -746,7 +746,7 @@
     <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_VelikaGorica_HRV,CO2Cap</t>
+    <t>e_VelikaGorica_HRV,h_VelikaGorica_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
@@ -755,7 +755,7 @@
     <t>ep_gas_combined_cycle_G100000400052-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Zagreb_HRV,CO2Cap</t>
+    <t>e_Zagreb_HRV,h_Zagreb_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100001031110-CHP_ccs-rf</t>
@@ -764,7 +764,7 @@
     <t>ep_gas_steam_turbine_G100000400055-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Kutina_HRV,CO2Cap</t>
+    <t>e_Kutina_HRV,h_Kutina_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_m_coal_subcritical_G100000108044_ccs-rf</t>
@@ -773,13 +773,13 @@
     <t>ep_oil_combined_cycle_G100000400056-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Sisak_HRV,CO2Cap</t>
+    <t>e_Sisak_HRV,h_Sisak_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_oil_combined_cycle_G100000400058-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Sesvete_HRV,CO2Cap</t>
+    <t>e_Sesvete_HRV,h_Sesveth_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_oil_combined_cycle_G100000400059-CHP_ccs-rf</t>
@@ -791,7 +791,7 @@
     <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Osijek_HRV,CO2Cap</t>
+    <t>e_Osijek_HRV,h_Osijek_HRV,CO2Cap</t>
   </si>
   <si>
     <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
@@ -1219,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4282D65-110E-4440-B10B-F484E4ABB221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B54CC9-AD09-4B30-B81B-F4AB062D5E42}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2229,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED9FECF-1F0A-4BCE-9843-357054952346}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F460E42-A408-4172-8E6F-FB2CFFA622C9}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4376,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2BA984-850C-4AB2-A92B-58BEE4DF1603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A64BB18-B0FC-4EAF-9139-CEF880C9AD4F}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7326,7 +7326,7 @@
         <v>33</v>
       </c>
       <c r="O59">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="Q59" t="s">
         <v>134</v>
@@ -7379,7 +7379,7 @@
         <v>33</v>
       </c>
       <c r="O60">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="Q60" t="s">
         <v>134</v>
@@ -7432,7 +7432,7 @@
         <v>33</v>
       </c>
       <c r="O61">
-        <v>0.17882039730553978</v>
+        <v>0.17882039730553981</v>
       </c>
       <c r="Q61" t="s">
         <v>134</v>
@@ -7568,7 +7568,7 @@
         <v>16</v>
       </c>
       <c r="T63" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U63" t="s">
         <v>136</v>
@@ -7630,7 +7630,7 @@
         <v>16</v>
       </c>
       <c r="T64" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U64" t="s">
         <v>136</v>
@@ -7754,7 +7754,7 @@
         <v>16</v>
       </c>
       <c r="T66" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U66" t="s">
         <v>136</v>
@@ -7816,7 +7816,7 @@
         <v>16</v>
       </c>
       <c r="T67" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U67" t="s">
         <v>136</v>
@@ -9433,7 +9433,7 @@
         <v>33</v>
       </c>
       <c r="O100">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.45">
@@ -9462,7 +9462,7 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.45">
@@ -9491,7 +9491,7 @@
         <v>33</v>
       </c>
       <c r="O102">
-        <v>0.17225936902451533</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.45">
@@ -10336,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E97075-98E3-41F3-B6EB-10D10949CFEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF2118C-C0D3-42A8-8707-22825B33FEA7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0C31763-B926-4AF3-A75C-4DFEC4D4DFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA66F675-40DD-439E-B823-6436269431A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01D61C49-94EB-47B1-B781-E71D41C62138}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8EEAA1DC-1879-43E7-B166-E0881D3030F4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08B54CC9-AD09-4B30-B81B-F4AB062D5E42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357DEF6D-C07C-48BE-BDEB-60B01C7AEF8D}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2229,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F460E42-A408-4172-8E6F-FB2CFFA622C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C12C8A2-07DF-43BF-A243-668BEAEA18D9}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4376,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A64BB18-B0FC-4EAF-9139-CEF880C9AD4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0557A5-23C7-48FA-AF50-1A797D07DD15}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7326,7 +7326,7 @@
         <v>33</v>
       </c>
       <c r="O59">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="Q59" t="s">
         <v>134</v>
@@ -7379,7 +7379,7 @@
         <v>33</v>
       </c>
       <c r="O60">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="Q60" t="s">
         <v>134</v>
@@ -7432,7 +7432,7 @@
         <v>33</v>
       </c>
       <c r="O61">
-        <v>0.17882039730553981</v>
+        <v>0.17882039730553978</v>
       </c>
       <c r="Q61" t="s">
         <v>134</v>
@@ -8560,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="T79" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U79" t="s">
         <v>136</v>
@@ -8622,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="T80" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U80" t="s">
         <v>136</v>
@@ -9433,7 +9433,7 @@
         <v>33</v>
       </c>
       <c r="O100">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.45">
@@ -9462,7 +9462,7 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.45">
@@ -9491,7 +9491,7 @@
         <v>33</v>
       </c>
       <c r="O102">
-        <v>0.17225936902451539</v>
+        <v>0.17225936902451541</v>
       </c>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.45">
@@ -10336,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF2118C-C0D3-42A8-8707-22825B33FEA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739D932F-325D-448C-92A7-117B2D630B09}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA66F675-40DD-439E-B823-6436269431A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51422D00-3D23-4D7E-9CE9-7D11F80D9ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8EEAA1DC-1879-43E7-B166-E0881D3030F4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8B4E4CC4-0604-4CD2-9972-2227538035CB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357DEF6D-C07C-48BE-BDEB-60B01C7AEF8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006442F5-1D24-4C7E-BDAD-8FC09758D97F}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2229,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C12C8A2-07DF-43BF-A243-668BEAEA18D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BADC0D-AEA8-4BF9-9610-8201FD81F3B4}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4376,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0557A5-23C7-48FA-AF50-1A797D07DD15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B3B92C-1342-40B4-B735-D98061E8A391}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7568,7 +7568,7 @@
         <v>16</v>
       </c>
       <c r="T63" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U63" t="s">
         <v>136</v>
@@ -7630,7 +7630,7 @@
         <v>16</v>
       </c>
       <c r="T64" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U64" t="s">
         <v>136</v>
@@ -7754,7 +7754,7 @@
         <v>16</v>
       </c>
       <c r="T66" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U66" t="s">
         <v>136</v>
@@ -7816,7 +7816,7 @@
         <v>16</v>
       </c>
       <c r="T67" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U67" t="s">
         <v>136</v>
@@ -8560,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="T79" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U79" t="s">
         <v>136</v>
@@ -8622,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="T80" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U80" t="s">
         <v>136</v>
@@ -9433,7 +9433,7 @@
         <v>33</v>
       </c>
       <c r="O100">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.45">
@@ -9462,7 +9462,7 @@
         <v>33</v>
       </c>
       <c r="O101">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.45">
@@ -9491,7 +9491,7 @@
         <v>33</v>
       </c>
       <c r="O102">
-        <v>0.17225936902451541</v>
+        <v>0.17225936902451539</v>
       </c>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.45">
@@ -10336,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739D932F-325D-448C-92A7-117B2D630B09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1CC0ED-453B-4C98-B46E-90C709369AAD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
+++ b/VerveStacks_HRV_grids_kan10/vt_vervestacks_HRV_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51422D00-3D23-4D7E-9CE9-7D11F80D9ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6DF4554-64E6-4C8B-BBD8-0486C8C121CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8B4E4CC4-0604-4CD2-9972-2227538035CB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3F05C1CF-7431-4C5B-A9E6-B0A0478BAC50}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006442F5-1D24-4C7E-BDAD-8FC09758D97F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7669BCA8-56DB-4F5F-BDB9-64F29D1B59DB}">
   <dimension ref="B9:V25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2229,7 +2229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BADC0D-AEA8-4BF9-9610-8201FD81F3B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AA3A4C-E7C2-431F-B104-452E90BF5F94}">
   <dimension ref="B9:X46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4376,7 +4376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B3B92C-1342-40B4-B735-D98061E8A391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B16CE3E0-A76F-4B08-88ED-4D401AE664AF}">
   <dimension ref="B9:X124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7568,7 +7568,7 @@
         <v>16</v>
       </c>
       <c r="T63" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="U63" t="s">
         <v>136</v>
@@ -7630,7 +7630,7 @@
         <v>16</v>
       </c>
       <c r="T64" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="U64" t="s">
         <v>136</v>
@@ -10336,7 +10336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1CC0ED-453B-4C98-B46E-90C709369AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB6372CC-037C-4DC9-A357-368F1E738360}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
